--- a/automated_scripts/reviews_catalog.xlsx
+++ b/automated_scripts/reviews_catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4859,7 +4859,6 @@
           <t>cool,I love it</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
         <v>5</v>
       </c>
@@ -5055,7 +5054,6 @@
           <t>I love this style so much, so cute.</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
         <v>5</v>
       </c>
@@ -5091,7 +5089,6 @@
           <t>good shoes</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
         <v>5</v>
       </c>
@@ -5127,7 +5124,6 @@
           <t>It looks very comfortable.</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
         <v>5</v>
       </c>
@@ -5243,7 +5239,6 @@
           <t>The shoes are very comfortable and warm.</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
         <v>5</v>
       </c>
@@ -5799,7 +5794,6 @@
           <t>The shoes are very comfortable and fit my feet well.</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
         <v>5</v>
       </c>
@@ -5875,7 +5869,6 @@
           <t>So cute, soft and warm.I love it very much.</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
         <v>5</v>
       </c>
@@ -5911,7 +5904,6 @@
           <t>Talla bastante pequeño, unas 2 tallas</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
         <v>3</v>
       </c>
@@ -5947,7 +5939,6 @@
           <t>Très bien taille petit</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
         <v>5</v>
       </c>
@@ -5983,7 +5974,6 @@
           <t>He pedido la talla más grande, y aun así son bastante más pequeñas de lo esperado</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
         <v>3</v>
       </c>
@@ -6019,7 +6009,6 @@
           <t>The slippers are of good quality and suitable for wearing in the living room, the shoes are soft and warm, I decided to buy back another pair to my husband, I sincerely recommend</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
         <v>5</v>
       </c>
@@ -6055,7 +6044,6 @@
           <t xml:space="preserve">Súper calentitas y cómodas. </t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
         <v>5</v>
       </c>
@@ -6091,7 +6079,6 @@
           <t>super buenas,calientes y de gran calidad</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
         <v>5</v>
       </c>
@@ -6127,7 +6114,6 @@
           <t>I like to wear these shoes at work because it's so comfortable and it's warm.</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
         <v>5</v>
       </c>
@@ -6163,7 +6149,6 @@
           <t>The slippers are warm, the price is suitable, and it makes me feel like my feet are soft to wear, especially for the bedroom I recommend</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
         <v>5</v>
       </c>
@@ -6199,7 +6184,6 @@
           <t>Все супер, розмір на мій 38, 38-39 підійшов.</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
         <v>5</v>
       </c>
@@ -6235,7 +6219,6 @@
           <t>vallen kleiner dan wat de maat aangeeft.</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
         <v>3</v>
       </c>
@@ -6271,7 +6254,6 @@
           <t>It's cool.Love it.</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
         <v>5</v>
       </c>
@@ -6307,7 +6289,6 @@
           <t>For the price, shoes are good and ship fast.</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>5</v>
       </c>
@@ -6343,7 +6324,6 @@
           <t>Shoes are very comfortable.</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
         <v>5</v>
       </c>
@@ -6379,7 +6359,6 @@
           <t>love this new slippers</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
         <v>5</v>
       </c>
@@ -6415,7 +6394,6 @@
           <t>the shoes are so cool</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="n">
         <v>5</v>
       </c>
@@ -6451,7 +6429,6 @@
           <t>The shlippers are really soft.</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="n">
         <v>5</v>
       </c>
@@ -6487,7 +6464,6 @@
           <t>Very nice shoes, good quality.</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
         <v>5</v>
       </c>
@@ -6523,7 +6499,6 @@
           <t>Very comfortable and sell well.</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
         <v>5</v>
       </c>
@@ -6559,7 +6534,6 @@
           <t>Absolutely love these sandals! The colorblock design is super stylish, and the thick bottom makes them really comfortable for walking. Perfect for summer outings!</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
         <v>5</v>
       </c>
@@ -6596,7 +6570,6 @@
 </t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
         <v>5</v>
       </c>
@@ -6632,7 +6605,6 @@
           <t>The shoes is good,it's my love style.</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
         <v>5</v>
       </c>
@@ -6668,7 +6640,6 @@
           <t>Cool Shoes!</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="n">
         <v>5</v>
       </c>
@@ -6704,7 +6675,6 @@
           <t>The shoes are soft.</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
         <v>5</v>
       </c>
@@ -6860,7 +6830,6 @@
           <t>cute shoes and ship fast</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
         <v>5</v>
       </c>
@@ -6896,7 +6865,6 @@
           <t>Хорошая обувь, мягкая и удобная.</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
         <v>5</v>
       </c>
@@ -6932,13 +6900,2110 @@
           <t>So cute slippers, so love it.</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
         <v>5</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>E***x</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ecwco5a67wefmxfpfzpktv7b</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Comfortable and Soft Slippers Indeed</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>nice slippers and soft</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="n">
+        <v>5</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>N***a</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>rbpbt0g6nlsuar65cug1m9ak</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Soft and Comfortable Experience Guaranteed</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Very soft and comfortable.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="n">
+        <v>5</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Z***w</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>svhvv0bhqbmqrwyxhbfm8mxq</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Adorable Soft Shoes for Comfort</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>so cute shoes and soft to wear</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>O***e</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>mon0nbt2y7ri7kjnjjvoecl4</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>A Warm and Inviting Atmosphere</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>It looks so warm</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://oss-cf.cjdropshipping.com/other/2024/10/14/09/48741d8b-bcf7-44fa-b2f0-afbbc7c8dd72.jpg</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>5</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>U***w</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>bemz344z177xxn9xja25i6h6</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Warm and Comfortable Living Space Tips</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Very warm and comfortable.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="n">
+        <v>5</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>U***f</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>f0s9bcbeo98plfk26ak57iaq</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Warm and Good Experience Always.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Very warm, very good.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="n">
+        <v>5</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>E***j</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0ot2vzg8px6b9uvtylvbbdum</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Children Adore These Cute Shoes</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Cute shoes, my children love it.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="n">
+        <v>5</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>F***p</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>hh4pm4r8azw7vhfng8uzm9v3</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Adorable Slippers Perfect for Comfort</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>So cute slipper</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="n">
+        <v>5</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2024-11-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>X***k</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>97udst0ln2m5u3nl21xjps2y</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Soft and Comfortable Fabric Choice</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>It's soft and comfortable.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>B***x</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>xsg9nia9xob6yrknc5z91oyk</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Comfortable Shoes for Everyday Wear</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Comfortable shoes</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="n">
+        <v>5</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2025-01-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>M***x</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>n4ldxvssv9px6op48ec3it0x</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Comfortable and Good Experience Awaiting</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Good and comfortable.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="n">
+        <v>5</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Z***o</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>fdcuyob4oac9yhf3yrl7964z</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Colorful Product, Fast Delivery, Great Quality</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>I like the color and it look good, it come fast</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-accelerate.aliyuncs.com/298aeb46-8525-42ba-9251-7779e574f73a.jpg,https://cc-west-usa.oss-accelerate.aliyuncs.com/4c3c5176-2f23-41fa-8bd1-4d5085d220de.jpg</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>5</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Z***d</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>7e04as03g9a4a0raw8qr7590</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>High-Quality Fabric: Great Look, Feel</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>The quality of the fabric was good, looks and feels great</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="n">
+        <v>5</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>I***k</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>6nfjw6i5ahwtmum5eg6srps8</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Son's Choice: Great Fitting Jeans</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>My son actually picked these out on his own. They fit great on him and the quality is good. Nice color jeans too.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="n">
+        <v>5</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>F***g</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>6nfjw6i5ahwtmum5eg6srps8</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Perfect Size I Was Seeking</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Just the size I was looking for thanks
+</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="n">
+        <v>5</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>J***j</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>6nfjw6i5ahwtmum5eg6srps8</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>High Quality Material and Color</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Very nice, nice materiel, great color I will definitely order another one
+</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="n">
+        <v>5</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>K***y</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>oh25ka3k1oag0zi8gxfvubcg</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Cool Style Received Quickly and Effectively</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>The style is cool and received quickly</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="n">
+        <v>5</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>D***z</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>8ngdnto4r6xmm02y6ukrozom</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>High-Quality Goods and Excellent Service</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"The quality of the official store goods is good, and the fabric is also very good. The workmanship is fine, the thread ends are clean, and the size is standard. The Asian size is 2-3 sizes smaller than the European size, and the service is also very good. I am very satisfied
+"
+</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2023-11-28/ebc57981-7c34-4809-96d2-d78680128b1c.jpg,https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2023-11-28/d84adf23-ba09-49b8-a73a-b5fcd66fd500.jpg,https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2023-11-28/144e01b7-0dc8-40ea-96c6-d406b3297a18.jpg</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>5</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>2023-11-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>X***b</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>raunggsdmd5h073pvqcnpjii</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Good Advice Without Quotation Marks</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>It's good</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
+        <v>5</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>V***j</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>6dbka0xr0snpgr9h4mnl26xh</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Soft Texture with Acceptable Thickness</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Soft and the thickness is ok.</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="n">
+        <v>5</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>S***y</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>q2g5dz0x20gz7gr43yl6jyh1</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Thick and High-Quality Material Review</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Very thick and good quality.</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://oss-cf.cjdropshipping.com/other/2024/10/21/07/d0ebe423-e6cb-4744-b020-4fac54ae5e7c.jpg</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>5</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>U***h</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>bwkg562vw939lsfpivjt31i2</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Light, Soft, Warm: Perfect Comfort Blend</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>It's light but soft and warm.</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>D***x</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Super Wisiorki: A Unique Experience</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>super wisiorki</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="n">
+        <v>5</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Z***p</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>I Loved It So Much</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>me encanto</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/ce905a28-2e4f-4c62-b78b-3dd333c6a391.jpg</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>5</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>U***i</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Fast Arrival, Excellent Service Experience</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>llego muy rapido que buen servicio</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>5</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Z***e</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Authentic Stones Exactly As Described</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>real stones just as described.</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/73edd3cd-a1d2-4983-8e59-a9778d0ee389.jpg,https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/8d73ea66-a826-43df-a763-a01dbe334ed2.jpg,https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/e61c75c0-a05e-4d43-805b-9aadac5d3c54.jpg</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>5</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>X***i</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Adorable and Charming All Around You</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>cute</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="n">
+        <v>5</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>X***i</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>As I Imagined It Would Be</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>comme j'imaginais</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="n">
+        <v>5</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>S***s</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Impressive Design With Thoughtful Aesthetics</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>great design</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="n">
+        <v>5</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>B***r</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Great Product, Highly Recommend This Store</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>buen producto recomiendo ésta tienda</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="n">
+        <v>5</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>K***y</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Beautiful Just Like In The Photo</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>lindo como en la foto</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="n">
+        <v>5</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>L***f</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Excellent Keychains, Great Quality Guaranteed</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>excelente los llaveros bue a calidad</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="n">
+        <v>5</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>R***m</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Very Beautiful and Charming Design</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>muy lindo</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="n">
+        <v>5</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>N***u</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Beautiful and Charming All Around</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>super bonito</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="n">
+        <v>5</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>C***w</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Great Size, Material, and Style</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>buen tamaño, material y bonito</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="n">
+        <v>5</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>K***f</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Excellent Material and Very Beautiful</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>excelente material y muy lindo</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="n">
+        <v>5</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>P***j</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Grateful for Your Kindness and Support</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Thank you.</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/a0db8656-8f6e-4283-917e-5280183258a5.jpg,https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/84a664ea-7f53-4c80-a767-3a50a150be1a.jpg</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>5</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Q***f</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Delivery Time Described as Very Delayed</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Es como se describe.  muy demorada la entrega</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="n">
+        <v>5</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>H***o</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Absolutely Fantastic Experience, Highly Recommend!</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>super</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="n">
+        <v>5</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>2024-06-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Z***z</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Mastering the Art of Communication</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="n">
+        <v>5</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>R***z</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Satisfied with Refund, No Images</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>No hay imágenes,  no lo recibí,  pero estoy muy satisfecha, el vendedor lo reembolso sin inconvenientes. No calificare el artículo,  ni la fecha de entrega</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>E***u</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Very Beautiful and Exquisite Moments</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>muy hermoso</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/311c5d30-9239-4532-b120-15ea4060e614.jpg</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>5</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>T***r</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Order Not Received, Need Assistance</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>order not received</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>D***c</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Order Not Received, Money Lost</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>pedido no recibido
+ahora nadie responde 
+perdí mi dinero 😔</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>E***m</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Appreciation for Excellent Trade Service</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>thanks for the trade and very good service</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="n">
+        <v>5</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>2024-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>N***z</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Creative Solutions for Everyday Challenges</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>genial</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="n">
+        <v>5</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Z***z</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Quality Content That Impresses Everyone</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>جيده</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="n">
+        <v>3</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>E***n</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Great Products, Excellent Service Experienced</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Product description was on target: very pretty. The products arrived in excellent shape and in a timely manner. Would do business again.</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>K***t</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Excellent Product, Timely Delivery, Highly Recommend</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Product description was on target: very pretty. The products arrived in excellent shape and in a timely manner. Would do business again.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="n">
+        <v>5</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>T***r</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Thank You for Your Excellent Service</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>B.jr merci ho vendeur et  CJ  très satisfait j'ai bien reçu votre commande merci beaucoup</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="n">
+        <v>5</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>H***o</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Beautiful Piece for Its Price</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Для своей цены пойдёт. Красивая штука. Есть ли там натуральные камни, вопрос. :)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/8963544e-72fc-4808-8dcb-fd8024f764c3.jpg,https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/e722f2e4-1a73-458b-a191-6bc6d0423d73.jpg</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>4</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>I***z</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Unexpectedly Large and Beautiful Pendants</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Muy bonitos los colgante, me lo esperaba más pequeño, pero es más grande de lo que pesaba, a la familia le gusta</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://cc-west-usa.oss-us-west-1.aliyuncs.com/comment/additional/0001/image/2024-09-05/7bbdba0f-bfdf-4848-8a87-cfb4d561eddd.jpg</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>5</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>A***z</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Ultimate Excellence Redefined in Full</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>fuulll best of the best</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="n">
+        <v>5</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>V***k</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Rapid Delivery Without Any Delays</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Very fast delivery</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="n">
+        <v>5</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>C***t</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>It Never Came, Just Empty Promises</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>It never came.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>N***t</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Great Product Worth Every Penny</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ótimo produto</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="n">
+        <v>5</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>R***p</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>27g0ig1pmlvub18es0kro3z1</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Exceptional Value for Your Money</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>good for value.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="n">
+        <v>4</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
         </is>
       </c>
     </row>
